--- a/Testcase Template.xlsx
+++ b/Testcase Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kvaluentaxa2026\axa2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7AAEF-CF49-464E-A819-5C49C0BB2B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A806175C-0132-4F67-8BF8-F445E0516D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>TESTID</t>
   </si>
@@ -102,14 +102,52 @@
     <t>Executed By</t>
   </si>
   <si>
-    <t>AX1.01.T005</t>
+    <t>AX1.01.T006</t>
+  </si>
+  <si>
+    <t>Verify Valid Login with valid Image Captcha</t>
+  </si>
+  <si>
+    <t>UN: XYZ
+PWD: ABC1234
+Captcha Code : As displayed in the Captcha</t>
+  </si>
+  <si>
+    <t>It should redirect to dashboard page</t>
+  </si>
+  <si>
+    <t>AX1.02.T005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verfiy Valid Email </t>
+  </si>
+  <si>
+    <t>1.Enter email in the email field or text box</t>
+  </si>
+  <si>
+    <t>abc@xyz.com , ab15@sdef.in</t>
+  </si>
+  <si>
+    <t>No error message realted to format of email</t>
+  </si>
+  <si>
+    <t>Verfiy Invalid Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter invalid email in the email filed </t>
+  </si>
+  <si>
+    <t>abxc@in, 13243434gmail.com</t>
+  </si>
+  <si>
+    <t>Error message should get displayed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +182,13 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -191,7 +236,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -201,8 +246,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -226,8 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="9"/>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="10">
+    <cellStyle name="Hyperlink" xfId="9" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -538,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D296902-3B7C-4F5F-9463-5B1A83149691}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -556,7 +604,7 @@
       </c>
       <c r="B1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -616,7 +664,7 @@
     </row>
     <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>7</v>
@@ -633,9 +681,58 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
+    <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D11" r:id="rId1" display="abc@xyz.com" xr:uid="{45A018C2-34D3-44E4-9257-C7AABE7FA51C}"/>
+    <hyperlink ref="D12" r:id="rId2" xr:uid="{5CE610FB-43FA-45CE-A8AF-0151195D2038}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
